--- a/data/trans_orig/CLASESOCIAL_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social de la persona entrevistada en 2007</t>
+          <t>Población según la clase social de la persona entrevistada en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>184057</t>
+          <t>182002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>235784</t>
+          <t>235853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>952846</t>
+          <t>952255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1016826</t>
+          <t>1014824</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1140586</t>
+          <t>1144901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1238207</t>
+          <t>1237110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>539763</t>
+          <t>539472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>605114</t>
+          <t>600882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218403</t>
+          <t>220899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273555</t>
+          <t>276867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>771634</t>
+          <t>772869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>865700</t>
+          <t>863924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>127832</t>
+          <t>128696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172332</t>
+          <t>174567</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62763</t>
+          <t>61704</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171878</t>
+          <t>172684</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225966</t>
+          <t>225569</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29525</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55555</t>
+          <t>54387</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>46551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78712</t>
+          <t>79741</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47555</t>
+          <t>46033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76398</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25592</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61381</t>
+          <t>61346</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>95468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362785</t>
+          <t>364879</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>432827</t>
+          <t>433605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722451</t>
+          <t>722403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>804935</t>
+          <t>801759</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1108211</t>
+          <t>1103055</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1215962</t>
+          <t>1219383</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>583606</t>
+          <t>579946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659719</t>
+          <t>657731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>383071</t>
+          <t>390015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>454509</t>
+          <t>456412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>988971</t>
+          <t>987940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089938</t>
+          <t>1089551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>307134</t>
+          <t>308472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>374384</t>
+          <t>373379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92026</t>
+          <t>92362</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132080</t>
+          <t>132195</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>413730</t>
+          <t>414835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>490151</t>
+          <t>493704</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193645</t>
+          <t>193916</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>254308</t>
+          <t>252377</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221120</t>
+          <t>219329</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>278152</t>
+          <t>275923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430419</t>
+          <t>427435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512061</t>
+          <t>510155</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92227</t>
+          <t>91529</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131696</t>
+          <t>133325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33005</t>
+          <t>32890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60438</t>
+          <t>60034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132124</t>
+          <t>131856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179379</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32431</t>
+          <t>33593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58739</t>
+          <t>60154</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>53755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84900</t>
+          <t>86481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93643</t>
+          <t>94498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135956</t>
+          <t>133766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35794</t>
+          <t>35706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61288</t>
+          <t>62191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34705</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63112</t>
+          <t>65486</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78876</t>
+          <t>77632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115337</t>
+          <t>117066</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17145</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>44222</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77097</t>
+          <t>77986</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>83480</t>
+          <t>84592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123038</t>
+          <t>121333</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>88709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>121522</t>
+          <t>123056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182707</t>
+          <t>182686</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237024</t>
+          <t>238463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281088</t>
+          <t>279967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>328750</t>
+          <t>327418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>223891</t>
+          <t>224450</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267838</t>
+          <t>267874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516072</t>
+          <t>516104</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>582360</t>
+          <t>584435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>605068</t>
+          <t>599812</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>699147</t>
+          <t>697472</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1754126</t>
+          <t>1758722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1869461</t>
+          <t>1874330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2390502</t>
+          <t>2386371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2541052</t>
+          <t>2546137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1180579</t>
+          <t>1177587</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1298417</t>
+          <t>1295040</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>671714</t>
+          <t>669763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>762070</t>
+          <t>761631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1880987</t>
+          <t>1877946</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2033894</t>
+          <t>2030559</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>502803</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>586888</t>
+          <t>587079</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144650</t>
+          <t>142595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195890</t>
+          <t>194139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>661673</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>757502</t>
+          <t>763155</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>331636</t>
+          <t>332112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>405546</t>
+          <t>405521</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>335700</t>
+          <t>338076</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>407234</t>
+          <t>412182</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>690387</t>
+          <t>689070</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>794725</t>
+          <t>795843</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>434428</t>
+          <t>435160</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>513171</t>
+          <t>516845</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>276827</t>
+          <t>278822</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>345732</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>731355</t>
+          <t>730490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>836446</t>
+          <t>841847</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social de la persona entrevistada en 2012</t>
+          <t>Población según la clase social de la persona entrevistada en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245987</t>
+          <t>245000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>303604</t>
+          <t>304042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>977306</t>
+          <t>977483</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1043113</t>
+          <t>1044181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1239047</t>
+          <t>1242382</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1336237</t>
+          <t>1336288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388166</t>
+          <t>390568</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451631</t>
+          <t>451759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151492</t>
+          <t>152462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>201937</t>
+          <t>202797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>555416</t>
+          <t>557397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>646005</t>
+          <t>642156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183783</t>
+          <t>182600</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>237001</t>
+          <t>234876</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84253</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123381</t>
+          <t>123785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275327</t>
+          <t>276747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>345361</t>
+          <t>345432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40997</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41379</t>
+          <t>40592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42390</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72511</t>
+          <t>73041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28993</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54287</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>6967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22100</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40739</t>
+          <t>41152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70894</t>
+          <t>70428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>426355</t>
+          <t>425977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>501696</t>
+          <t>501692</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>732269</t>
+          <t>729975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>821962</t>
+          <t>820092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1184194</t>
+          <t>1186358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1299856</t>
+          <t>1302492</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648116</t>
+          <t>642397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>734424</t>
+          <t>731181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503213</t>
+          <t>497506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582474</t>
+          <t>582906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1175597</t>
+          <t>1177350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1293982</t>
+          <t>1286702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350297</t>
+          <t>350045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>422398</t>
+          <t>423333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126899</t>
+          <t>123806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>175496</t>
+          <t>173375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>490924</t>
+          <t>494088</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>577809</t>
+          <t>578746</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242786</t>
+          <t>242702</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306511</t>
+          <t>305470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188590</t>
+          <t>186999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245668</t>
+          <t>245044</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>444467</t>
+          <t>446254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>529738</t>
+          <t>534545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125464</t>
+          <t>124753</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175749</t>
+          <t>174984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53536</t>
+          <t>55287</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89245</t>
+          <t>89841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190859</t>
+          <t>192116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250373</t>
+          <t>252862</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52454</t>
+          <t>53971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63390</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96577</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100068</t>
+          <t>100598</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143015</t>
+          <t>141984</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>31432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61105</t>
+          <t>60849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34591</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62538</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>71873</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112927</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46581</t>
+          <t>47817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16148</t>
+          <t>17162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>30575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58452</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96397</t>
+          <t>96052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>137862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>74812</t>
+          <t>76142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112991</t>
+          <t>112924</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>183539</t>
+          <t>184053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>237729</t>
+          <t>239013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221947</t>
+          <t>220434</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270144</t>
+          <t>268435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>208328</t>
+          <t>207769</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>255232</t>
+          <t>251257</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445510</t>
+          <t>445319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511618</t>
+          <t>511840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>726174</t>
+          <t>727756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>829904</t>
+          <t>827873</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1808137</t>
+          <t>1812272</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1931125</t>
+          <t>1934034</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2562359</t>
+          <t>2563665</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2732416</t>
+          <t>2736805</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1101297</t>
+          <t>1099831</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1211925</t>
+          <t>1212226</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>715794</t>
+          <t>718288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>816654</t>
+          <t>814580</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1848799</t>
+          <t>1846977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2000472</t>
+          <t>2004493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>585931</t>
+          <t>580013</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>673290</t>
+          <t>678771</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>229013</t>
+          <t>229375</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>295539</t>
+          <t>290459</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>830977</t>
+          <t>831094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>947090</t>
+          <t>942853</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>379030</t>
+          <t>378144</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>458925</t>
+          <t>460242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>294824</t>
+          <t>298312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>375909</t>
+          <t>376328</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>700940</t>
+          <t>698048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>811238</t>
+          <t>815084</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>397893</t>
+          <t>400599</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>481560</t>
+          <t>483679</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280256</t>
+          <t>280062</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348139</t>
+          <t>352402</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>697841</t>
+          <t>698760</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>807668</t>
+          <t>801707</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social de la persona entrevistada en 2016</t>
+          <t>Población según la clase social de la persona entrevistada en 2016 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241184</t>
+          <t>242529</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293308</t>
+          <t>296375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>771408</t>
+          <t>772359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>822526</t>
+          <t>824337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1026108</t>
+          <t>1023650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1108853</t>
+          <t>1106122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294105</t>
+          <t>293742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>348220</t>
+          <t>348643</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>119938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>165556</t>
+          <t>164397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>425687</t>
+          <t>423880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>501072</t>
+          <t>499180</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108564</t>
+          <t>109492</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149629</t>
+          <t>149072</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>26124</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51187</t>
+          <t>52465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>138697</t>
+          <t>141410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187964</t>
+          <t>187943</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2789</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18779</t>
+          <t>18267</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40061</t>
+          <t>39651</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>13398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31843</t>
+          <t>32314</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>530681</t>
+          <t>529579</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>611571</t>
+          <t>609520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>887835</t>
+          <t>886785</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>981421</t>
+          <t>977397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1441692</t>
+          <t>1435908</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1560340</t>
+          <t>1562123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>736412</t>
+          <t>739841</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>832902</t>
+          <t>830263</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568039</t>
+          <t>566080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>653145</t>
+          <t>649419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1335913</t>
+          <t>1333946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1457662</t>
+          <t>1451520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>326050</t>
+          <t>328631</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>395277</t>
+          <t>400285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95912</t>
+          <t>92114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140436</t>
+          <t>135234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431097</t>
+          <t>436134</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>516640</t>
+          <t>518457</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>207351</t>
+          <t>208643</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>271606</t>
+          <t>269968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>228415</t>
+          <t>226619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289540</t>
+          <t>289205</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454614</t>
+          <t>457817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>541814</t>
+          <t>540204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>95587</t>
+          <t>98121</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>140557</t>
+          <t>141081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57670</t>
+          <t>56462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89944</t>
+          <t>89052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162428</t>
+          <t>161988</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217041</t>
+          <t>215990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48515</t>
+          <t>48720</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78833</t>
+          <t>79164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70260</t>
+          <t>69268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104744</t>
+          <t>105989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128479</t>
+          <t>127846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172306</t>
+          <t>175334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28182</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53344</t>
+          <t>54033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57636</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>92705</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>92569</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133852</t>
+          <t>133385</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22767</t>
+          <t>22063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>45995</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34397</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61313</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98272</t>
+          <t>96547</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>139165</t>
+          <t>136988</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>86891</t>
+          <t>89532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>125117</t>
+          <t>126723</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>195988</t>
+          <t>195846</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>250923</t>
+          <t>252573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>266759</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>319131</t>
+          <t>315906</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247406</t>
+          <t>247875</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294455</t>
+          <t>295399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531276</t>
+          <t>532908</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>601618</t>
+          <t>600918</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>851798</t>
+          <t>847529</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>953919</t>
+          <t>953688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1755508</t>
+          <t>1750359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1874853</t>
+          <t>1870658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2638930</t>
+          <t>2624465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2803708</t>
+          <t>2789604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1085102</t>
+          <t>1093185</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1201833</t>
+          <t>1201631</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>773340</t>
+          <t>767971</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>875428</t>
+          <t>869692</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1893125</t>
+          <t>1896863</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2038996</t>
+          <t>2043792</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>474634</t>
+          <t>480244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>563065</t>
+          <t>567468</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139727</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>191209</t>
+          <t>191879</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>637384</t>
+          <t>634763</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>736372</t>
+          <t>736270</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>341239</t>
+          <t>338511</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>418002</t>
+          <t>413635</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>333984</t>
+          <t>331911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>408302</t>
+          <t>407082</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,47 +9086,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>745344</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>693390</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>798938</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>10,07%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>11,6%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>745344</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>696207</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>798027</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>386194</t>
+          <t>388303</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>466140</t>
+          <t>466799</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>313066</t>
+          <t>312596</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>385764</t>
+          <t>384943</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>724769</t>
+          <t>722459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>828797</t>
+          <t>832650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Clase social de la persona entrevistada en 2023</t>
+          <t>Población según la clase social de la persona entrevistada en 2023 (tasa de respuesta: 97,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149923</t>
+          <t>149890</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188469</t>
+          <t>190693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>567292</t>
+          <t>566446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>599519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>722900</t>
+          <t>719604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>779815</t>
+          <t>782038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>221099</t>
+          <t>224190</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264625</t>
+          <t>264673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91574</t>
+          <t>91947</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118592</t>
+          <t>119018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>321146</t>
+          <t>320283</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>375940</t>
+          <t>379286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>55771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82927</t>
+          <t>85043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48872</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91857</t>
+          <t>93173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>125652</t>
+          <t>126013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>10679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,82 +9964,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9558</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5798</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15550</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>26641</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>19525</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>36258</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>2,12%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,96%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9558</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5568</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15079</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>26641</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>19368</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>36833</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16235</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>28275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>352044</t>
+          <t>364764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>593629</t>
+          <t>592680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>686893</t>
+          <t>698280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1097999</t>
+          <t>1091822</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1159220</t>
+          <t>1195198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1661583</t>
+          <t>1651371</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>471351</t>
+          <t>529875</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>835150</t>
+          <t>839221</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645115</t>
+          <t>645266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1218486</t>
+          <t>1200977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319766</t>
+          <t>1297741</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1955753</t>
+          <t>1980274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>355326</t>
+          <t>355670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1136974</t>
+          <t>999729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83845</t>
+          <t>84359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138454</t>
+          <t>140981</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>446944</t>
+          <t>449521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1434723</t>
+          <t>1462066</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205542</t>
+          <t>217147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>363644</t>
+          <t>364213</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>149685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263661</t>
+          <t>266133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>427251</t>
+          <t>426482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>614635</t>
+          <t>611189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81760</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153233</t>
+          <t>153782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>57293</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>100291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158997</t>
+          <t>159436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242422</t>
+          <t>243786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>26621</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53842</t>
+          <t>56693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45700</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75283</t>
+          <t>76247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79083</t>
+          <t>80787</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120433</t>
+          <t>119520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40579</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85085</t>
+          <t>87922</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48386</t>
+          <t>48059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75993</t>
+          <t>75408</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98531</t>
+          <t>98786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149492</t>
+          <t>150868</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19262</t>
+          <t>18756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>42196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19577</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>31046</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56353</t>
+          <t>55424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>104840</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150248</t>
+          <t>146546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127358</t>
+          <t>128694</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164007</t>
+          <t>165031</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>244380</t>
+          <t>243039</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300378</t>
+          <t>299954</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>342873</t>
+          <t>341852</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>396583</t>
+          <t>394552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336404</t>
+          <t>336872</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>382154</t>
+          <t>380943</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>692076</t>
+          <t>696331</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>762120</t>
+          <t>762925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>562126</t>
+          <t>573624</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>801598</t>
+          <t>798438</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1309843</t>
+          <t>1319611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1736085</t>
+          <t>1737993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2003208</t>
+          <t>2037114</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2506121</t>
+          <t>2505045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>809518</t>
+          <t>817327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1133641</t>
+          <t>1141499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>794244</t>
+          <t>798135</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1432892</t>
+          <t>1512682</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1789826</t>
+          <t>1776068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2501005</t>
+          <t>2451719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>445071</t>
+          <t>447004</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1225133</t>
+          <t>1226444</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>137798</t>
+          <t>137964</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>192421</t>
+          <t>193497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>593706</t>
+          <t>592119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1771660</t>
+          <t>1613258</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>345942</t>
+          <t>349467</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>503304</t>
+          <t>503600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>307716</t>
+          <t>298136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>426062</t>
+          <t>423804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>716397</t>
+          <t>713210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>910817</t>
+          <t>909830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>398386</t>
+          <t>400689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>562256</t>
+          <t>560105</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>369519</t>
+          <t>365266</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>498172</t>
+          <t>494621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>810091</t>
+          <t>818957</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1035730</t>
+          <t>1036711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CLASESOCIAL_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CLASESOCIAL_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>182002</t>
+          <t>182445</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>235853</t>
+          <t>234632</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>952255</t>
+          <t>952195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1014824</t>
+          <t>1016252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1144901</t>
+          <t>1143857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1237110</t>
+          <t>1240772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>539472</t>
+          <t>537864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>600882</t>
+          <t>602041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220899</t>
+          <t>217658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276867</t>
+          <t>276456</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>772869</t>
+          <t>766843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>863924</t>
+          <t>861821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128696</t>
+          <t>128856</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174567</t>
+          <t>172598</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>34141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61704</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>173517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225569</t>
+          <t>224663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29934</t>
+          <t>30615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54387</t>
+          <t>54853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30939</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46551</t>
+          <t>48405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79741</t>
+          <t>80343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>45834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75734</t>
+          <t>76321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10930</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61346</t>
+          <t>61760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95468</t>
+          <t>97158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>364879</t>
+          <t>361718</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433605</t>
+          <t>432628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722403</t>
+          <t>721281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>801759</t>
+          <t>802414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1103055</t>
+          <t>1107080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1219383</t>
+          <t>1218135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579946</t>
+          <t>578972</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>657731</t>
+          <t>659653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390015</t>
+          <t>386310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>456412</t>
+          <t>456167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>987940</t>
+          <t>985022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1089551</t>
+          <t>1095249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>308472</t>
+          <t>309131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>373379</t>
+          <t>375546</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92362</t>
+          <t>91997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132195</t>
+          <t>132515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414835</t>
+          <t>413724</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>493704</t>
+          <t>489012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193916</t>
+          <t>198488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>252377</t>
+          <t>252679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>219329</t>
+          <t>220622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275923</t>
+          <t>279012</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>430762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>510155</t>
+          <t>512592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91529</t>
+          <t>90950</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133325</t>
+          <t>132884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>33373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60034</t>
+          <t>59234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131856</t>
+          <t>132563</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180593</t>
+          <t>180086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33593</t>
+          <t>32633</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60154</t>
+          <t>59973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53755</t>
+          <t>54245</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>84242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94498</t>
+          <t>92431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133766</t>
+          <t>133921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62191</t>
+          <t>62178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65486</t>
+          <t>63667</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77632</t>
+          <t>77230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117066</t>
+          <t>115567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>36673</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>67387</t>
+          <t>65640</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>17967</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>45174</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77986</t>
+          <t>77689</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>84592</t>
+          <t>83431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>121333</t>
+          <t>122924</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>88709</t>
+          <t>87193</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>123056</t>
+          <t>123835</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>182686</t>
+          <t>182462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>238463</t>
+          <t>234527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279967</t>
+          <t>278320</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>327418</t>
+          <t>327667</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>224450</t>
+          <t>224035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>267874</t>
+          <t>268353</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516104</t>
+          <t>515596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584435</t>
+          <t>582969</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599812</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>697472</t>
+          <t>695898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1758722</t>
+          <t>1756835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1874330</t>
+          <t>1872386</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2386371</t>
+          <t>2389734</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2546137</t>
+          <t>2548391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1177587</t>
+          <t>1182260</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1295040</t>
+          <t>1291882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>669763</t>
+          <t>668407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761631</t>
+          <t>764210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1877946</t>
+          <t>1884986</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2030559</t>
+          <t>2031048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>502803</t>
+          <t>499735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>587079</t>
+          <t>586623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>142595</t>
+          <t>146100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>194139</t>
+          <t>193396</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>664154</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>763155</t>
+          <t>763618</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>332112</t>
+          <t>329431</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>405521</t>
+          <t>403656</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>338076</t>
+          <t>335875</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>412182</t>
+          <t>408246</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>689070</t>
+          <t>689287</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>795843</t>
+          <t>790287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>435160</t>
+          <t>432486</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>516845</t>
+          <t>515032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>278822</t>
+          <t>273465</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>340539</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>730490</t>
+          <t>736393</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>841847</t>
+          <t>841043</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>245000</t>
+          <t>244027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304042</t>
+          <t>301483</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>977483</t>
+          <t>981685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1044181</t>
+          <t>1046272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1242382</t>
+          <t>1235622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1336288</t>
+          <t>1337164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390568</t>
+          <t>388732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>451759</t>
+          <t>453580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152462</t>
+          <t>151487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202797</t>
+          <t>204815</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>557397</t>
+          <t>556592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>642156</t>
+          <t>643188</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>182600</t>
+          <t>180870</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>234876</t>
+          <t>234751</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83809</t>
+          <t>85393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>123785</t>
+          <t>125332</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>276747</t>
+          <t>279935</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>345432</t>
+          <t>346215</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17932</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>40867</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>19644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40592</t>
+          <t>41235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43455</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73041</t>
+          <t>75605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29019</t>
+          <t>29478</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56342</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6967</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21804</t>
+          <t>22722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>41152</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70428</t>
+          <t>72138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>425977</t>
+          <t>422601</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>501692</t>
+          <t>499888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>729975</t>
+          <t>734091</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>820092</t>
+          <t>825044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1186358</t>
+          <t>1179944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1302492</t>
+          <t>1292809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642397</t>
+          <t>643706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>731181</t>
+          <t>729899</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>497506</t>
+          <t>500039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582906</t>
+          <t>582840</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1177350</t>
+          <t>1169066</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1286702</t>
+          <t>1288954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350045</t>
+          <t>349904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>423333</t>
+          <t>423789</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>123806</t>
+          <t>124792</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>173375</t>
+          <t>176402</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494088</t>
+          <t>493297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>578746</t>
+          <t>583464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>242702</t>
+          <t>241393</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>305470</t>
+          <t>308919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186999</t>
+          <t>187125</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>244034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446254</t>
+          <t>441136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534545</t>
+          <t>530876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124753</t>
+          <t>126100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174984</t>
+          <t>174780</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55287</t>
+          <t>54416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89841</t>
+          <t>89083</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192116</t>
+          <t>193722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>252862</t>
+          <t>256860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29305</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53971</t>
+          <t>54018</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63836</t>
+          <t>63418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100598</t>
+          <t>98384</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141984</t>
+          <t>142133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31432</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>58904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>34084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62155</t>
+          <t>60655</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71873</t>
+          <t>73781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>113627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47817</t>
+          <t>46350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30575</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>56815</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96052</t>
+          <t>96906</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>137862</t>
+          <t>137753</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76142</t>
+          <t>75659</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112924</t>
+          <t>111553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>184053</t>
+          <t>183427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239013</t>
+          <t>239622</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220434</t>
+          <t>222384</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268435</t>
+          <t>268969</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207769</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251257</t>
+          <t>254643</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>445319</t>
+          <t>439011</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511840</t>
+          <t>507183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>46,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>727756</t>
+          <t>728962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>827873</t>
+          <t>831902</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1812272</t>
+          <t>1807260</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1934034</t>
+          <t>1930502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2563665</t>
+          <t>2568095</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2736805</t>
+          <t>2736355</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1099831</t>
+          <t>1101683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1212226</t>
+          <t>1215603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>718288</t>
+          <t>718638</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>814580</t>
+          <t>818906</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1846977</t>
+          <t>1836167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2004493</t>
+          <t>1992336</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>580013</t>
+          <t>583189</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>678771</t>
+          <t>678458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>229375</t>
+          <t>228756</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>290459</t>
+          <t>293958</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>831094</t>
+          <t>831919</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>942853</t>
+          <t>945564</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>378144</t>
+          <t>377973</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>460242</t>
+          <t>461324</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>298312</t>
+          <t>300524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>376328</t>
+          <t>376490</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>698048</t>
+          <t>697746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>815084</t>
+          <t>807548</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>400599</t>
+          <t>396991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>483679</t>
+          <t>478585</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280062</t>
+          <t>279926</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>352402</t>
+          <t>353621</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>698760</t>
+          <t>697788</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>801707</t>
+          <t>805697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>242529</t>
+          <t>245001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>296375</t>
+          <t>295729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>772359</t>
+          <t>772229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>824337</t>
+          <t>826314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1023650</t>
+          <t>1026327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1106122</t>
+          <t>1109522</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,69%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293742</t>
+          <t>294059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>348643</t>
+          <t>349782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>119938</t>
+          <t>117784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164397</t>
+          <t>165629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>423880</t>
+          <t>424060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499180</t>
+          <t>499786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109492</t>
+          <t>108132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149072</t>
+          <t>147491</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26124</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>52465</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>141410</t>
+          <t>140632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>187943</t>
+          <t>188872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30843</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16983</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18267</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39651</t>
+          <t>41447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32314</t>
+          <t>32441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>529579</t>
+          <t>532275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>609520</t>
+          <t>610274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>886785</t>
+          <t>881055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>977397</t>
+          <t>974168</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1435908</t>
+          <t>1441064</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1562123</t>
+          <t>1564261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739841</t>
+          <t>736952</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>830263</t>
+          <t>829044</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>566080</t>
+          <t>568713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>649419</t>
+          <t>655996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1333946</t>
+          <t>1333365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1451520</t>
+          <t>1454565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>328631</t>
+          <t>328000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>400285</t>
+          <t>394190</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92114</t>
+          <t>96214</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135234</t>
+          <t>137205</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>436134</t>
+          <t>433100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>518457</t>
+          <t>519629</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208643</t>
+          <t>210461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>269968</t>
+          <t>268399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226619</t>
+          <t>225497</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289205</t>
+          <t>288830</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>457817</t>
+          <t>452918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>540204</t>
+          <t>540689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98121</t>
+          <t>98523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141081</t>
+          <t>141927</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56462</t>
+          <t>56506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89052</t>
+          <t>89905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>161988</t>
+          <t>165050</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>215990</t>
+          <t>218834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48720</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79164</t>
+          <t>78586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>69783</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105989</t>
+          <t>104151</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127846</t>
+          <t>126790</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175334</t>
+          <t>171751</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27778</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54033</t>
+          <t>54680</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>59153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92705</t>
+          <t>91147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92569</t>
+          <t>91526</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133385</t>
+          <t>133745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22063</t>
+          <t>22378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45995</t>
+          <t>46099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>23251</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33821</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>96547</t>
+          <t>98723</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136988</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>89532</t>
+          <t>87376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126723</t>
+          <t>123676</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>195846</t>
+          <t>196209</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252573</t>
+          <t>249392</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266759</t>
+          <t>269596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315906</t>
+          <t>316034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247875</t>
+          <t>248517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295399</t>
+          <t>294569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532908</t>
+          <t>532394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>600918</t>
+          <t>598127</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>847529</t>
+          <t>853859</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>953688</t>
+          <t>954689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1750359</t>
+          <t>1757315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1870658</t>
+          <t>1877469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2624465</t>
+          <t>2638957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2789604</t>
+          <t>2808924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1093185</t>
+          <t>1087687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1201631</t>
+          <t>1200991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>767971</t>
+          <t>771519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>869692</t>
+          <t>871671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1896863</t>
+          <t>1885042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2043792</t>
+          <t>2042781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>480244</t>
+          <t>480219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>567468</t>
+          <t>566615</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>139964</t>
+          <t>141477</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>191879</t>
+          <t>191179</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>634763</t>
+          <t>640207</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>736270</t>
+          <t>741240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338511</t>
+          <t>338018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>413635</t>
+          <t>417230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331911</t>
+          <t>336779</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>407082</t>
+          <t>409820</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>693390</t>
+          <t>690871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>798938</t>
+          <t>799453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>388303</t>
+          <t>390342</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>466799</t>
+          <t>469621</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>312596</t>
+          <t>313210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384943</t>
+          <t>386030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>722459</t>
+          <t>724606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>832650</t>
+          <t>832332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>168631</t>
+          <t>201308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149890</t>
+          <t>178965</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190693</t>
+          <t>223773</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>582962</t>
+          <t>629891</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>566446</t>
+          <t>611154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>599519</t>
+          <t>647789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>751593</t>
+          <t>831199</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>719604</t>
+          <t>795529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>782038</t>
+          <t>862697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,36%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>244123</t>
+          <t>264709</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224190</t>
+          <t>241488</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264673</t>
+          <t>288385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>104999</t>
+          <t>119265</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91947</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119018</t>
+          <t>135296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>349122</t>
+          <t>383974</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>320283</t>
+          <t>355950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>379286</t>
+          <t>418890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69122</t>
+          <t>76822</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85043</t>
+          <t>93494</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49026</t>
+          <t>53177</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>108171</t>
+          <t>118814</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93173</t>
+          <t>100747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126013</t>
+          <t>137006</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>16419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19525</t>
+          <t>20237</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36258</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28275</t>
+          <t>31039</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>509078</t>
+          <t>572194</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>509078</t>
+          <t>572194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>509078</t>
+          <t>572194</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>745588</t>
+          <t>811311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>745588</t>
+          <t>811311</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745588</t>
+          <t>811311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1254666</t>
+          <t>1383505</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1254666</t>
+          <t>1383505</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1254666</t>
+          <t>1383505</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>506734</t>
+          <t>556067</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>364764</t>
+          <t>506354</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>592680</t>
+          <t>609729</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>955939</t>
+          <t>971458</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>698280</t>
+          <t>931521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1091822</t>
+          <t>1013492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1462673</t>
+          <t>1527526</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1195198</t>
+          <t>1461451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1651371</t>
+          <t>1594494</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>730686</t>
+          <t>798827</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529875</t>
+          <t>748059</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>839221</t>
+          <t>856480</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>810722</t>
+          <t>665702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645266</t>
+          <t>629462</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1200977</t>
+          <t>704330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1541408</t>
+          <t>1464529</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1297741</t>
+          <t>1403079</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1980274</t>
+          <t>1532132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>570172</t>
+          <t>359856</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>355670</t>
+          <t>321659</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>999729</t>
+          <t>398593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>115741</t>
+          <t>129932</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84359</t>
+          <t>113034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>140981</t>
+          <t>148564</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>685914</t>
+          <t>489788</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>449521</t>
+          <t>449704</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1462066</t>
+          <t>534497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>308865</t>
+          <t>329968</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>217147</t>
+          <t>294091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364213</t>
+          <t>363445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>227467</t>
+          <t>253282</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149685</t>
+          <t>229289</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>266133</t>
+          <t>281183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>536333</t>
+          <t>583250</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>426482</t>
+          <t>542218</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>611189</t>
+          <t>627193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>123856</t>
+          <t>134330</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>110695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153782</t>
+          <t>159508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79499</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57293</t>
+          <t>76987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100291</t>
+          <t>110350</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>203355</t>
+          <t>226778</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159436</t>
+          <t>198246</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>243786</t>
+          <t>259622</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2240314</t>
+          <t>2179048</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2240314</t>
+          <t>2179048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2240314</t>
+          <t>2179048</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2189369</t>
+          <t>2112822</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2189369</t>
+          <t>2112822</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2189369</t>
+          <t>2112822</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4429683</t>
+          <t>4291870</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4429683</t>
+          <t>4291870</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4429683</t>
+          <t>4291870</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39035</t>
+          <t>45510</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26621</t>
+          <t>31964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56693</t>
+          <t>69072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59389</t>
+          <t>71405</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44869</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76247</t>
+          <t>90843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>116916</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80787</t>
+          <t>94480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119520</t>
+          <t>141911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>65028</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41469</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87922</t>
+          <t>85317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>48059</t>
+          <t>59022</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75408</t>
+          <t>88790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>119580</t>
+          <t>140051</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98786</t>
+          <t>116836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>150868</t>
+          <t>164305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28970</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>24099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>24270</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>50507</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29605</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55424</t>
+          <t>68557</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>124848</t>
+          <t>133446</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>104840</t>
+          <t>113769</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>146546</t>
+          <t>157991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>145555</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128694</t>
+          <t>139915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165031</t>
+          <t>180311</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>270403</t>
+          <t>293045</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243039</t>
+          <t>266660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>299954</t>
+          <t>324246</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>370029</t>
+          <t>403418</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>341852</t>
+          <t>374076</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>394552</t>
+          <t>431452</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>358948</t>
+          <t>386062</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336872</t>
+          <t>363226</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>380943</t>
+          <t>411594</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>728976</t>
+          <t>789480</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>696331</t>
+          <t>748458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>762925</t>
+          <t>822037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>620842</t>
+          <t>682336</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>620842</t>
+          <t>682336</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>620842</t>
+          <t>682336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>637633</t>
+          <t>707663</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>637633</t>
+          <t>707663</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>637633</t>
+          <t>707663</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1258474</t>
+          <t>1389999</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1258474</t>
+          <t>1389999</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1258474</t>
+          <t>1389999</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>714400</t>
+          <t>802886</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>573624</t>
+          <t>737771</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>798438</t>
+          <t>859865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1598290</t>
+          <t>1672755</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1319611</t>
+          <t>1616278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1737993</t>
+          <t>1727450</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2312690</t>
+          <t>2475640</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2037114</t>
+          <t>2390085</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2505045</t>
+          <t>2558841</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1032768</t>
+          <t>1128564</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>817327</t>
+          <t>1067420</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1141499</t>
+          <t>1192361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977342</t>
+          <t>859991</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>798135</t>
+          <t>812871</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1512682</t>
+          <t>902909</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2010110</t>
+          <t>1988554</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1776068</t>
+          <t>1913994</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2451719</t>
+          <t>2067801</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>447004</t>
+          <t>430948</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1226444</t>
+          <t>515085</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>137964</t>
+          <t>167539</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193497</t>
+          <t>213647</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>592119</t>
+          <t>612297</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1613258</t>
+          <t>704417</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>450797</t>
+          <t>481095</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>440212</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>503600</t>
+          <t>522599</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>298136</t>
+          <t>388889</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>423804</t>
+          <t>455930</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>10,71%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>8,35%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>833377</t>
+          <t>904238</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>713210</t>
+          <t>852308</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>909830</t>
+          <t>961392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>504004</t>
+          <t>549422</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>400689</t>
+          <t>503705</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>560105</t>
+          <t>592841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>365266</t>
+          <t>452460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>494621</t>
+          <t>528165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>951471</t>
+          <t>1037832</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>818957</t>
+          <t>980561</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1036711</t>
+          <t>1104503</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3370233</t>
+          <t>3433578</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3572590</t>
+          <t>3631796</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6942823</t>
+          <t>7065373</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
